--- a/artfynd/S 3528-2025 artfynd.xlsx
+++ b/artfynd/S 3528-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY200"/>
+  <dimension ref="A1:AZ200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533246</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69537140</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1035,6 +1050,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533207</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1156,6 +1176,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533208</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1277,6 +1302,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533214</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1398,6 +1428,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533217</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1519,6 +1554,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533218</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1640,6 +1680,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533220</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1761,6 +1806,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533234</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1882,6 +1932,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533243</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2003,6 +2058,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533247</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2124,6 +2184,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533271</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2234,6 +2299,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99739624</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2355,6 +2425,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533209</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2476,6 +2551,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533215</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2597,6 +2677,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533216</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2718,6 +2803,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533219</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2839,6 +2929,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533221</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2960,6 +3055,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533235</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3081,6 +3181,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533244</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3202,6 +3307,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533248</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3323,6 +3433,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533252</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3444,6 +3559,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533267</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3565,6 +3685,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533272</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3684,6 +3809,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66397090</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3795,6 +3925,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74624506</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3897,6 +4032,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120346590</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3999,6 +4139,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120346594</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4120,6 +4265,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69535245</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4241,6 +4391,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69537116</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4362,6 +4517,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69537127</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4483,6 +4643,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69537134</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4604,6 +4769,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69537174</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4725,6 +4895,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69537175</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4846,6 +5021,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69537151</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4967,6 +5147,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69537162</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5088,6 +5273,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533222</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5207,6 +5397,11 @@
       <c r="AY39" t="inlineStr">
         <is>
           <t>Trädinventeringen i Kalmar län</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533249</t>
         </is>
       </c>
     </row>
@@ -5329,6 +5524,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106548147</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5453,6 +5653,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122897561</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5577,6 +5782,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127936542</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5696,6 +5906,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130753087</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5816,6 +6031,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130867756</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5925,6 +6145,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90292612</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6034,6 +6259,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91035474</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6143,6 +6373,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91035597</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6266,6 +6501,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114041690</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6385,6 +6625,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92203071</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6504,6 +6749,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110608864</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6613,6 +6863,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131196538</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6722,6 +6977,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81837823</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6831,6 +7091,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90292654</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6946,6 +7211,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118782221</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7059,6 +7329,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81837840</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7168,6 +7443,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90292620</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7287,6 +7567,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110608767</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7417,6 +7702,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99219603</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7551,6 +7841,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99440174</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7678,6 +7973,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86650899</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7801,6 +8101,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123253345</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7920,6 +8225,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123752521</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8029,6 +8339,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91035549</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8148,6 +8463,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113763856</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8257,6 +8577,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90292659</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8376,6 +8701,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113763855</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8491,6 +8821,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118782167</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8606,6 +8941,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118782218</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8715,6 +9055,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91035590</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8834,6 +9179,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116507542</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8953,6 +9303,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93923588</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9062,6 +9417,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90292675</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9177,6 +9537,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97805836</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9296,6 +9661,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113763860</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9415,6 +9785,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125524353</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9534,6 +9909,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93923584</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9643,6 +10023,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81837845</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9758,6 +10143,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121805374</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9867,6 +10257,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91035668</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9982,6 +10377,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121805368</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -10101,6 +10501,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116507535</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10210,6 +10615,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81837847</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10329,6 +10739,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93923726</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10448,6 +10863,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117795022</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10567,6 +10987,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117795050</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10676,6 +11101,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91035681</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10795,6 +11225,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123752534</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10914,6 +11349,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97049626</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -11034,6 +11474,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132537549</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -11155,6 +11600,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124274039</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -11280,6 +11730,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87058388</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11393,6 +11848,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107950991</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11512,6 +11972,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123041965</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11631,6 +12096,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123752516</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11750,6 +12220,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113763893</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11871,6 +12346,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125602478</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11977,6 +12457,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74977282</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -12083,6 +12568,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74977283</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -12185,6 +12675,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120346554</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -12289,6 +12784,11 @@
       <c r="AY100" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74150319</t>
         </is>
       </c>
     </row>
@@ -12391,6 +12891,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16043146</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12497,6 +13002,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74152728</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12626,6 +13136,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93924075</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12732,6 +13247,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74768362</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12834,6 +13354,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120346586</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12950,6 +13475,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2767170</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -13056,6 +13586,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74983767</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -13162,6 +13697,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74983768</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -13264,6 +13804,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76634527</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -13362,6 +13907,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108623282</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13460,6 +14010,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108770224</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13562,6 +14117,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120346533</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13664,6 +14224,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120346534</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13766,6 +14331,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120346536</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13868,6 +14438,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120346540</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13970,6 +14545,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120346542</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -14072,6 +14652,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120346556</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -14174,6 +14759,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120346560</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -14276,6 +14866,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120346564</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14378,6 +14973,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120346571</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14489,6 +15089,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120346572</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14591,6 +15196,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120346575</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14697,6 +15307,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74469985</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14799,6 +15414,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120346574</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14901,6 +15521,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120346577</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -15015,6 +15640,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67084687</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -15121,6 +15751,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75144027</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -15227,6 +15862,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75144028</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15329,6 +15969,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76634524</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15431,6 +16076,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76634529</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15533,6 +16183,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76634530</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15635,6 +16290,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76634532</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15737,6 +16397,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76634534</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15853,6 +16518,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85885121</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15955,6 +16625,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120346530</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -16057,6 +16732,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120346587</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -16163,6 +16843,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75133225</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -16279,6 +16964,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85885062</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -16385,6 +17075,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74081091</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16510,6 +17205,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120687141</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16630,6 +17330,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120687142</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16750,6 +17455,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120687144</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16875,6 +17585,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120687147</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16991,6 +17706,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120687148</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -17097,6 +17817,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74209116</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -17221,6 +17946,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116507690</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -17327,6 +18057,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74723941</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -17429,6 +18164,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120346589</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -17531,6 +18271,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76634525</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17633,6 +18378,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76634528</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17735,6 +18485,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76634531</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17837,6 +18592,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76634533</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17961,6 +18721,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92202568</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -18071,6 +18836,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124003182</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -18177,6 +18947,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132697183</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -18287,6 +19062,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67084695</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -18392,6 +19172,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7268921</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -18499,6 +19284,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755546</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -18606,6 +19396,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755547</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18713,6 +19508,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755548</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18820,6 +19620,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755549</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18927,6 +19732,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755550</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -19034,6 +19844,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755551</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -19141,6 +19956,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755552</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -19248,6 +20068,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755553</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -19355,6 +20180,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755554</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -19462,6 +20292,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755555</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -19569,6 +20404,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755556</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -19676,6 +20516,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755557</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -19792,6 +20637,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97717608</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -19914,6 +20764,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67886106</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -20033,6 +20888,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81719378</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -20156,6 +21016,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59240651</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -20272,6 +21137,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/20355333</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -20388,6 +21258,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/20354649</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -20507,6 +21382,11 @@
           <t>Fiskpredatorer i fredningsområden</t>
         </is>
       </c>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123459791</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -20630,6 +21510,11 @@
           <t>Fiskpredatorer i fredningsområden</t>
         </is>
       </c>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123691721</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -20741,6 +21626,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/20524285</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -20860,6 +21750,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124201166</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -20976,6 +21871,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/20355181</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -21092,6 +21992,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/20355332</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -21208,6 +22113,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/26653337</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -21319,6 +22229,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/35164712</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -21435,6 +22350,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/30117220</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -21554,6 +22474,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132786475</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -21669,6 +22594,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81719391</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -21788,6 +22718,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121805336</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -21899,6 +22834,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/20537810</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -22015,6 +22955,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/31732119</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -22134,6 +23079,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77027309</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -22253,6 +23203,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124201172</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -22366,6 +23321,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61231794</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -22477,6 +23437,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/20538016</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -22588,6 +23553,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/44076678</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -22704,6 +23674,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/20354683</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -22823,6 +23798,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121805405</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -22942,6 +23922,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86327146</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -23058,6 +24043,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/20354427</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -23177,6 +24167,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77132940</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -23296,8 +24291,214 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124201169</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>